--- a/02_加值成品/生物/生物2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物2-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物2-1 養分與酵素　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物2-1 養分與酵素　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>提供主要能量的養分是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>醣類</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>澱粉</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>供能</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>建構與修補身體的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>蛋白質</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>使失去活性</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>化學反應</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>鈣鐵等</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>建構</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>儲存能量的養分是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>脂質</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>酸鹼度</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>儲能</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>生物體內的催化劑是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>酵素</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>鈣鐵等</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>維生素礦物質</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>催化</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>酵素的本質是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>蛋白質</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>蛋白</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>調節生理但不供能的是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>鈣鐵等</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>維生素礦物質</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>澱粉</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>六大養分中最多的是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>調節生理</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>使失去活性</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>占比高</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>酵素能加快什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>化學反應</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>使失去活性</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>澱粉</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>速率</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>缺乏會導致貧血的礦物質是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>維生素礦物質</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>調節生理</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>鐵</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>礦物質</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>缺乏會影響骨骼牙齒的礦物質？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>鈣</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>酸鹼度</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>礦物質</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物2-1 養分與酵素　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物2-1 養分與酵素　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>維生素主要功能是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>調節生理</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>維生素礦物質</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不會可重複用</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>非供能</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>酵素一種只作用一種受質稱？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>鈣</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>澱粉</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>專一性</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>專一</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>高溫對酵素的影響？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>使失去活性</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>化學反應</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>鈣鐵等</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>維生素礦物質</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>失活</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>酵素用完會消失嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>不會可重複用</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>維生素礦物質</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>鈣</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>酵素</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>催化劑</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>鳳梨使肉變嫩因含？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>蛋白質分解酵素</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>各有不同功能缺一影響健康</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>適溫最佳過高會使蛋白質變性失活</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>高溫使酵素失活影響代謝</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>酵素</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>缺乏維生素可能導致？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>疾病(如壞血病)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>各有不同功能缺一影響健康</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>低溫降低酵素與微生物活性</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>其結構只與特定受質吻合</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>缺乏症</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>礦物質的例子？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>不會可重複用</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>調節生理</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>鈣鐵等</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>酵素</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>礦物</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>酵素活性也受什麼影響？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>酸鹼度</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>維生素礦物質</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>pH</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>唾液中的消化酵素分解哪種養分？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>使失去活性</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>酵素</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>澱粉</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>澱粉酶</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>酵素作用有最適的什麼條件？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>使失去活性</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>鈣</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>溫度與酸鹼</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>最適</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物2-1 養分與酵素　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物2-1 養分與酵素　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何酵素具有專一性？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>其結構只與特定受質吻合</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>疾病(如壞血病)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>高溫使蛋白質變性</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>低溫降低酵素與微生物活性</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>結構</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>說明溫度如何影響酵素活性？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>蛋白質分解酵素</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>適溫最佳過高會使蛋白質變性失活</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>將大分子分解為可吸收小分子</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>大幅加快生理反應使其在體溫下進行</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>溫度</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>為何均衡攝取六大養分很重要？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>將大分子分解為可吸收小分子</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>低溫降低酵素與微生物活性</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>各有不同功能缺一影響健康</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>疾病(如壞血病)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>均衡</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>酵素為催化劑對反應速率的意義？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>大幅加快生理反應使其在體溫下進行</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>蛋白質分解酵素</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>疾病(如壞血病)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>高溫使酵素失活影響代謝</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>催化</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>發燒過高為何危險(從酵素角度)？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>高溫使酵素失活影響代謝</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>大幅加快生理反應使其在體溫下進行</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>其結構只與特定受質吻合</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>將大分子分解為可吸收小分子</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>失活</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>比較醣類蛋白質脂質的主要功能？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>醣供能蛋白建構脂質儲能</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>適溫最佳過高會使蛋白質變性失活</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>大幅加快生理反應使其在體溫下進行</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>疾病(如壞血病)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>酵素可重複使用的意義？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>少量酵素即可持續催化</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>疾病(如壞血病)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>高溫使蛋白質變性</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>適溫最佳過高會使蛋白質變性失活</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>效率</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>消化酵素如何幫助人體利用食物？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>將大分子分解為可吸收小分子</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>大幅加快生理反應使其在體溫下進行</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>適溫最佳過高會使蛋白質變性失活</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>高溫使酵素失活影響代謝</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>消化</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何冰箱冷藏能延長食物保存？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>其結構只與特定受質吻合</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>各有不同功能缺一影響健康</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>蛋白質分解酵素</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>低溫降低酵素與微生物活性</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>溫度</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>酵素是蛋白質對高溫敏感的原因？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>蛋白質分解酵素</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>低溫降低酵素與微生物活性</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>其結構只與特定受質吻合</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>高溫使蛋白質變性</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>變性</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物2-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>供能</t>
+          <t>主要供能：醣類是人體最主要的能量來源，像米飯、麵包都含有豐富的醣類</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>建構</t>
+          <t>建構修補：蛋白質是構成身體組織的重要材料，也能修補受損的細胞</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>儲能</t>
+          <t>儲存能量：脂質能把多餘的能量儲存起來，需要時再分解釋放出來使用</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>催化</t>
+          <t>生物催化劑：酵素能加快體內化學反應的速度，幫助生命活動順利進行</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>蛋白</t>
+          <t>本質是蛋白質：酵素的主要成分是蛋白質，所以會受到溫度與酸鹼度的影響</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節生理：維生素和礦物質不能提供能量，但能調節身體各種生理機能</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>占比高</t>
+          <t>占比最高：水約占人體重量的一大部分，是六大類養分中含量最多的一種</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>速率</t>
+          <t>加快反應：酵素能大幅提高體內化學反應進行的速度，是重要的催化劑</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>礦物質</t>
+          <t>礦物質：鐵是合成血紅素的重要原料，長期缺鐵會使紅血球攜氧能力下降，造成貧血</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>礦物質</t>
+          <t>礦物質：鈣是構成骨骼和牙齒的主要成分之一，缺鈣會使骨骼牙齒發育不良、變得脆弱</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>非供能</t>
+          <t>調節功能：維生素不能提供能量，主要功能是調節身體的各種生理機能</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>專一</t>
+          <t>專一性：每一種酵素通常只能作用在特定的一種受質上，這種特性稱為專一性</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>失活</t>
+          <t>高溫失活：溫度太高會破壞酵素的結構，使酵素失去原本催化反應的活性</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>催化劑</t>
+          <t>可重複使用：酵素本身不會在反應中被消耗掉，能重複發揮催化的作用</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>酵素</t>
+          <t>含分解酵素：鳳梨中含有能分解蛋白質的酵素，所以能使肉質變得軟嫩</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>缺乏症</t>
+          <t>引發疾病：長期缺乏某種維生素，身體生理機能失調，可能引發相關疾病</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>礦物</t>
+          <t>常見礦物質：鈣能強化骨骼、鐵能幫助造血，都是人體需要的重要礦物質</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>受酸鹼影響：除了溫度，環境的酸鹼度也會影響酵素能不能正常發揮作用</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>澱粉酶</t>
+          <t>澱粉酶：唾液中含有澱粉酶，能把食物中的澱粉分解成較小的醣類分子</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>最適</t>
+          <t>最適：每種酵素都有最適合作用的溫度和酸鹼度，在這個條件下酵素的作用效率最高，超過範圍效率就會下降</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>結構</t>
+          <t>結構決定：酵素的形狀構造只能和特定形狀的受質互相吻合，所以具有專一性</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>溫度</t>
+          <t>溫度影響：酵素在適合的溫度下作用最好，溫度過高會使蛋白質變性而失去活性</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>均衡</t>
+          <t>功能各異：六大類養分各自負責不同任務，缺少任何一種都可能影響身體健康</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>催化</t>
+          <t>加速反應：酵素能大幅加快化學反應速度，讓反應在體溫下也能快速順利進行</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>失活</t>
+          <t>影響代謝：體溫過高會使體內酵素失去活性，導致正常代謝反應無法順利進行</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>功能比較：醣類主要供給能量、蛋白質負責建構修補身體、脂質則負責儲存能量</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>效率</t>
+          <t>效率提升：因為酵素能重複使用，所以只需少量酵素就能持續催化大量反應</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>消化</t>
+          <t>幫助吸收：消化酵素能把食物中的大分子分解成小分子，身體才能吸收利用</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>溫度</t>
+          <t>溫度：低溫會降低食物中酵素的作用速率，也抑制微生物的生長繁殖，兩者共同減緩食物腐敗的速度</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>變性</t>
+          <t>變性：酵素的本質是蛋白質，遇到高溫時蛋白質的立體結構會被破壞（變性），導致酵素永久失去作用能力</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物2-1_三種難度測驗卷.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>維生素礦物質</t>
+          <t>酸鹼度</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>調節生理</t>
+          <t>酵素</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>醣類</t>
+          <t>蛋白質</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>脂質</t>
+          <t>蛋白質</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>醣類</t>
+          <t>水</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>不會可重複用</t>
+          <t>蛋白質</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>酵素</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>鈣鐵等</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>調節生理</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>鈣鐵等</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>酵素</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
